--- a/lab-standards/BSIA-lab-standard.xlsx
+++ b/lab-standards/BSIA-lab-standard.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DFT and Verification Eng" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applied Semiconductor Power" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Smart Systems Engineering" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semiconductor Testing Eng" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -103,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -136,6 +137,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3838,4 +3845,725 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15.17" customWidth="1" min="1" max="1"/>
+    <col width="33.13" customWidth="1" min="2" max="2"/>
+    <col width="13.72" customWidth="1" min="3" max="3"/>
+    <col width="13.72" customWidth="1" min="4" max="4"/>
+    <col width="13.72" customWidth="1" min="5" max="5"/>
+    <col width="13.72" customWidth="1" min="6" max="6"/>
+    <col width="13.72" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.35" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Course-wise Training Infrastructure and Facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Course Name:</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Semiconductor Testing Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26.85" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Number of Trainees:</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Course-wise Training Space (Theoretical Classroom, Workshop/ Lab/ Classroom cum Workshop)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Course Name</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>SICIP required space for 25 trainees</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52.2" customHeight="1">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Semiconductor Testing Engineering</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Computer Lab (400 sft) and Test &amp; Measurement Laboratory (700–800 sft) for 25 trainees</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Major Training Equipment and Training Facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="115.65" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>•The institute shall not use the same facilities for any other projects/organizations offering a similar course.
+•The institute must provide sufficient evidence to prove ownership of the proposed training equipment.
+The list denotes the minimum training equipment and facility required to effectively conduct training for a specific course. Additionally, the institute must ensure that all other necessary training tools, equipment, and furniture are available to meet the requirement of competency standards (CS) provided by SICIP.
+For the operation of training course on Semiconductor Testing Engineering, the institute must ensure the availability of at least 80% of the major training equipment and training facilities (according to the CS) to be eligible for SICIP training delivery. If the score is below 80%, the remaining equipment and facilities need to be installed before the commencement of the training.
+The institute will also provide all other hand tools and power tools as per CS for 25 trainees. Also, they will arrange adequate seating arrangement and classroom setup for the 25 trainees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26.85" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>S.N.</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Major Equipment and Training facilities</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Required facilities</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Available facilities</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Weights
+(out of 10)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Weighted scores</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="14.15" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Computer/Laptop (Trainer)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="9">
+        <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="14.15" customHeight="1">
+      <c r="A17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Printer</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="9">
+        <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="14.15" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Multimedia Projector</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="9">
+        <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="14.15" customHeight="1">
+      <c r="A19" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>High-performance Desktop/Laptop Workstation</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" s="9">
+        <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
+        <v/>
+      </c>
+      <c r="G19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="14.15" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>ATE Test Program Development Software (Advantest SmarTest Offline/Simulator or equivalent ATE simulation environment)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="9">
+        <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
+        <v/>
+      </c>
+      <c r="G20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="14.15" customHeight="1">
+      <c r="A21" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Data Analysis Software (Spreadsheet/Statistical/Scripting Tools)</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" s="9">
+        <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="14.15" customHeight="1">
+      <c r="A22" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Digital Multimeter</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="9">
+        <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
+        <v/>
+      </c>
+      <c r="G22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="14.15" customHeight="1">
+      <c r="A23" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>ESD-safe Workbench with ESD Mat and Wrist Strap</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="9">
+        <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="14.15" customHeight="1">
+      <c r="A24" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Sample IC Devices and Test Boards (Digital, Analog, Mixed-Signal)</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" s="9">
+        <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="14.15" customHeight="1">
+      <c r="A25" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Breadboard and Electronic Component Kits</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="9">
+        <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
+        <v/>
+      </c>
+      <c r="G25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="14.15" customHeight="1">
+      <c r="A26" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Digital Storage Oscilloscope</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F26" s="9">
+        <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="14.15" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>DC Regulated Power Supply</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="9">
+        <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="14.15" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Function/Signal Generator</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="9">
+        <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="14.15" customHeight="1">
+      <c r="A29" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Logic Analyzer</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" s="9">
+        <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="14.15" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Sample Loadboard/DUT Board and Socket Demonstration Kits</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="9">
+        <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="14.15" customHeight="1">
+      <c r="A31" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Probe Card and Test Fixture Illustration/Demonstration Set</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="9">
+        <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="14.15" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>ATE Access or Remote/Partner ATE Facility (Advantest V93000 or equivalent) for Demonstration</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F32" s="9">
+        <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>01 set</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="14.15" customHeight="1">
+      <c r="A33" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Sample Production Test Data Sets (STDF/CSV) with Analysis Templates</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="9">
+        <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>01 set</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="14.15" customHeight="1">
+      <c r="A34" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Internet Connectivity with Network Switch and Router</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="9">
+        <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
+        <v/>
+      </c>
+      <c r="G34" s="9" t="n"/>
+    </row>
+    <row r="35" ht="14.15" customHeight="1">
+      <c r="A35" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Central File/Storage Server</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" s="9">
+        <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="14.15" customHeight="1">
+      <c r="A36" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>First Aid and Fire Safety Equipment</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" s="9">
+        <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
+        <v/>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>01 set</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="15">
+        <f>SUM(E16:E36)</f>
+        <v/>
+      </c>
+      <c r="F37" s="15">
+        <f>SUM(F16:F36)</f>
+        <v/>
+      </c>
+      <c r="G37" s="13" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Score out of 100</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="15">
+        <f>F37/E37*100</f>
+        <v/>
+      </c>
+      <c r="G38" s="13" t="n"/>
+    </row>
+    <row r="39" ht="9.75" customHeight="1"/>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total achieved points out of 30  </t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="15">
+        <f>F38*30/100</f>
+        <v/>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A40:E40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/lab-standards/BSIA-lab-standard.xlsx
+++ b/lab-standards/BSIA-lab-standard.xlsx
@@ -645,7 +645,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -669,7 +669,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -693,7 +693,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -741,7 +741,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -765,7 +765,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -789,7 +789,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -813,7 +813,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -837,7 +837,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -861,7 +861,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -885,7 +885,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -909,7 +909,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -933,7 +933,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -957,7 +957,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -981,7 +981,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1005,7 +1005,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1029,7 +1029,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1053,7 +1053,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1077,7 +1077,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1101,7 +1101,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1109,18 +1109,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1129,7 +1129,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1146,11 +1146,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1314,7 +1314,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1338,7 +1338,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1362,7 +1362,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1386,7 +1386,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1410,7 +1410,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1434,7 +1434,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1458,7 +1458,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1482,7 +1482,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1506,7 +1506,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1530,7 +1530,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -1578,7 +1578,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1602,7 +1602,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1626,7 +1626,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -1650,7 +1650,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1674,7 +1674,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1698,7 +1698,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1722,7 +1722,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1746,7 +1746,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1770,7 +1770,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1778,18 +1778,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1798,7 +1798,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1815,11 +1815,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1983,7 +1983,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2007,7 +2007,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2031,7 +2031,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2055,7 +2055,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2079,7 +2079,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2103,7 +2103,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2127,7 +2127,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2151,7 +2151,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2175,7 +2175,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2199,7 +2199,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2223,7 +2223,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2247,7 +2247,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2271,7 +2271,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2295,7 +2295,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2319,7 +2319,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2343,7 +2343,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2367,7 +2367,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2391,7 +2391,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2415,7 +2415,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2439,7 +2439,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2447,18 +2447,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2467,7 +2467,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2484,11 +2484,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2652,7 +2652,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2676,7 +2676,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2700,7 +2700,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2724,7 +2724,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2748,7 +2748,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2772,7 +2772,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2796,7 +2796,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2820,7 +2820,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2844,7 +2844,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2868,7 +2868,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2892,7 +2892,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2916,7 +2916,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2940,7 +2940,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2964,7 +2964,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2988,7 +2988,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3012,7 +3012,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3036,7 +3036,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3060,7 +3060,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3084,7 +3084,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -3108,7 +3108,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3116,18 +3116,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3136,7 +3136,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -3144,7 +3144,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3153,11 +3153,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3321,7 +3321,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3345,7 +3345,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3369,7 +3369,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3393,7 +3393,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3417,7 +3417,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3441,7 +3441,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3465,7 +3465,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3513,7 +3513,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3537,7 +3537,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -3561,7 +3561,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3585,7 +3585,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3609,7 +3609,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3633,7 +3633,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3657,7 +3657,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3681,7 +3681,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3729,7 +3729,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3753,7 +3753,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="14" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -3777,7 +3777,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3785,18 +3785,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="10">
+      <c r="E35" s="15">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3805,7 +3805,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10">
+      <c r="F36" s="15">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3822,11 +3822,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10">
+      <c r="F38" s="15">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3912,6 +3912,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3924,6 +3928,10 @@
           <t>Computer Lab (400 sft) and Test &amp; Measurement Laboratory (700–800 sft) for 25 trainees</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3997,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -4021,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -4045,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>

--- a/lab-standards/BSIA-lab-standard.xlsx
+++ b/lab-standards/BSIA-lab-standard.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -137,6 +137,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -645,7 +657,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -669,7 +681,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -693,7 +705,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -717,7 +729,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -741,7 +753,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -765,7 +777,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -789,7 +801,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -813,7 +825,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -837,7 +849,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -861,7 +873,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -885,7 +897,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -909,7 +921,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -933,7 +945,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -957,7 +969,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -981,7 +993,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1005,7 +1017,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1029,7 +1041,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1053,7 +1065,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1077,7 +1089,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1101,7 +1113,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1109,18 +1121,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1129,7 +1141,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1137,7 +1149,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1146,11 +1158,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1314,7 +1326,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1338,7 +1350,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1362,7 +1374,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1386,7 +1398,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1410,7 +1422,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1434,7 +1446,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1458,7 +1470,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1482,7 +1494,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1506,7 +1518,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1530,7 +1542,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -1554,7 +1566,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -1578,7 +1590,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1602,7 +1614,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1626,7 +1638,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -1650,7 +1662,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1674,7 +1686,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1698,7 +1710,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1722,7 +1734,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1746,7 +1758,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1770,7 +1782,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1778,18 +1790,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1798,7 +1810,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1806,7 +1818,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1815,11 +1827,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1983,7 +1995,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2007,7 +2019,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2031,7 +2043,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2055,7 +2067,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2079,7 +2091,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2103,7 +2115,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2127,7 +2139,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2151,7 +2163,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2175,7 +2187,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2199,7 +2211,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2223,7 +2235,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2247,7 +2259,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2271,7 +2283,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2295,7 +2307,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2319,7 +2331,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2343,7 +2355,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2367,7 +2379,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2391,7 +2403,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2415,7 +2427,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2439,7 +2451,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2447,18 +2459,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2467,7 +2479,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -2475,7 +2487,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2484,11 +2496,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2652,7 +2664,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2676,7 +2688,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2700,7 +2712,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2724,7 +2736,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2748,7 +2760,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2772,7 +2784,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2796,7 +2808,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2820,7 +2832,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2844,7 +2856,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2868,7 +2880,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2892,7 +2904,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2916,7 +2928,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2940,7 +2952,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2964,7 +2976,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2988,7 +3000,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3012,7 +3024,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3036,7 +3048,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3060,7 +3072,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3084,7 +3096,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -3108,7 +3120,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3116,18 +3128,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3136,7 +3148,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -3144,7 +3156,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3153,11 +3165,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3321,7 +3333,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -3345,7 +3357,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -3369,7 +3381,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -3393,7 +3405,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -3417,7 +3429,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -3441,7 +3453,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -3465,7 +3477,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -3489,7 +3501,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -3513,7 +3525,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -3537,7 +3549,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -3561,7 +3573,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -3585,7 +3597,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3609,7 +3621,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -3633,7 +3645,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3657,7 +3669,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3681,7 +3693,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3705,7 +3717,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3729,7 +3741,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3753,7 +3765,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -3777,7 +3789,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3785,18 +3797,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="15">
+      <c r="E35" s="17">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="17">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3805,7 +3817,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="15">
+      <c r="F36" s="17">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -3813,7 +3825,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3822,11 +3834,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
+      <c r="F38" s="17">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G38" s="17" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3853,7 +3865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -3912,10 +3924,6 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3928,10 +3936,6 @@
           <t>Computer Lab (400 sft) and Test &amp; Measurement Laboratory (700–800 sft) for 25 trainees</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3990,22 +3994,22 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Computer/Laptop (Trainer)</t>
+          <t>High-performance Desktop/Laptop Workstation (25 trainees + 01 trainer)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -4014,7 +4018,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -4038,7 +4042,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -4062,12 +4066,12 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>High-performance Desktop/Laptop Workstation</t>
+          <t>ATE Test Program Development Software (Advantest SmarTest Offline/Simulator or equivalent ATE simulation environment)</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -4077,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -4086,12 +4090,12 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>ATE Test Program Development Software (Advantest SmarTest Offline/Simulator or equivalent ATE simulation environment)</t>
+          <t>Data Analysis Software (Spreadsheet/Statistical/Scripting Tools)</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
@@ -4101,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -4110,12 +4114,12 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Data Analysis Software (Spreadsheet/Statistical/Scripting Tools)</t>
+          <t>Digital Multimeter</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
@@ -4125,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -4134,12 +4138,12 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Digital Multimeter</t>
+          <t>ESD-safe Workbench with ESD Mat and Wrist Strap</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
@@ -4149,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -4158,12 +4162,12 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>ESD-safe Workbench with ESD Mat and Wrist Strap</t>
+          <t>Sample IC Devices and Test Boards (Digital, Analog, Mixed-Signal)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
@@ -4173,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -4182,12 +4186,12 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Sample IC Devices and Test Boards (Digital, Analog, Mixed-Signal)</t>
+          <t>Breadboard and Electronic Component Kits</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
@@ -4197,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -4206,22 +4210,22 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Breadboard and Electronic Component Kits</t>
+          <t>Digital Storage Oscilloscope</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -4230,12 +4234,12 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Digital Storage Oscilloscope</t>
+          <t>DC Regulated Power Supply</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
@@ -4245,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -4254,12 +4258,12 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>DC Regulated Power Supply</t>
+          <t>Function/Signal Generator</t>
         </is>
       </c>
       <c r="C27" s="9" t="n">
@@ -4278,12 +4282,12 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Function/Signal Generator</t>
+          <t>Logic Analyzer</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
@@ -4302,16 +4306,16 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Logic Analyzer</t>
+          <t>Sample Loadboard/DUT Board and Socket Demonstration Kits</t>
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>0</v>
@@ -4326,22 +4330,22 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Sample Loadboard/DUT Board and Socket Demonstration Kits</t>
+          <t>Probe Card and Test Fixture Illustration/Demonstration Set</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -4350,36 +4354,40 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Probe Card and Test Fixture Illustration/Demonstration Set</t>
+          <t>ATE Access or Remote/Partner ATE Facility (Advantest V93000 or equivalent) for Demonstration</t>
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F31" s="9">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
         <v/>
       </c>
-      <c r="G31" s="9" t="n"/>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>01 set</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ATE Access or Remote/Partner ATE Facility (Advantest V93000 or equivalent) for Demonstration</t>
+          <t>Sample Production Test Data Sets (STDF/CSV) with Analysis Templates</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
@@ -4389,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -4402,12 +4410,12 @@
       </c>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Sample Production Test Data Sets (STDF/CSV) with Analysis Templates</t>
+          <t>Internet Connectivity with Network Switch and Router</t>
         </is>
       </c>
       <c r="C33" s="9" t="n">
@@ -4417,25 +4425,21 @@
         <v>0</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F33" s="9">
         <f>IFERROR(MIN(C33,D33)*E33/C33,0)</f>
         <v/>
       </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>01 set</t>
-        </is>
-      </c>
+      <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Internet Connectivity with Network Switch and Router</t>
+          <t>Central File/Storage Server</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
@@ -4454,12 +4458,12 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="18" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Central File/Storage Server</t>
+          <t>First Aid and Fire Safety Equipment</t>
         </is>
       </c>
       <c r="C35" s="9" t="n">
@@ -4469,93 +4473,69 @@
         <v>0</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F35" s="9">
         <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
         <v/>
       </c>
-      <c r="G35" s="9" t="n"/>
-    </row>
-    <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="14" t="n">
-        <v>21</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>First Aid and Fire Safety Equipment</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F36" s="9">
-        <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
-        <v/>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>01 set</t>
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="19">
+        <f>SUM(E16:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="19">
+        <f>SUM(F16:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="13" t="n"/>
+    </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>Sum</t>
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>Score out of 100</t>
         </is>
       </c>
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="11" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="15">
-        <f>SUM(E16:E36)</f>
-        <v/>
-      </c>
-      <c r="F37" s="15">
-        <f>SUM(F16:F36)</f>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="19">
+        <f>F36/E36*100</f>
         <v/>
       </c>
       <c r="G37" s="13" t="n"/>
     </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>Score out of 100</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="15">
-        <f>F37/E37*100</f>
-        <v/>
-      </c>
-      <c r="G38" s="13" t="n"/>
-    </row>
-    <row r="39" ht="9.75" customHeight="1"/>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+    <row r="38" ht="9.75" customHeight="1"/>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
       </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="15">
-        <f>F38*30/100</f>
-        <v/>
-      </c>
-      <c r="G40" s="15" t="inlineStr">
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="19">
+        <f>F37*30/100</f>
+        <v/>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -4564,13 +4544,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lab-standards/BSIA-lab-standard.xlsx
+++ b/lab-standards/BSIA-lab-standard.xlsx
@@ -104,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -137,6 +137,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -657,7 +663,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -681,7 +687,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -705,7 +711,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -729,7 +735,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -753,7 +759,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -777,7 +783,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -801,7 +807,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -825,7 +831,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -849,7 +855,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -873,7 +879,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -897,7 +903,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -921,7 +927,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -945,7 +951,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -969,7 +975,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -993,7 +999,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1017,7 +1023,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1041,7 +1047,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1065,7 +1071,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1089,7 +1095,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1113,7 +1119,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1121,18 +1127,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="17">
+      <c r="E35" s="19">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1141,7 +1147,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="17">
+      <c r="F36" s="19">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1149,7 +1155,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1158,11 +1164,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="17">
+      <c r="F38" s="19">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1326,7 +1332,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1350,7 +1356,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1374,7 +1380,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1398,7 +1404,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -1422,7 +1428,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1446,7 +1452,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -1470,7 +1476,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1494,7 +1500,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1518,7 +1524,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1542,7 +1548,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -1566,7 +1572,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -1590,7 +1596,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -1614,7 +1620,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1638,7 +1644,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -1662,7 +1668,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1686,7 +1692,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1710,7 +1716,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1734,7 +1740,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1758,7 +1764,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1782,7 +1788,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1790,18 +1796,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="17">
+      <c r="E35" s="19">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1810,7 +1816,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="17">
+      <c r="F36" s="19">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -1818,7 +1824,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1827,11 +1833,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="17">
+      <c r="F38" s="19">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -1995,7 +2001,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2019,7 +2025,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2043,7 +2049,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2067,7 +2073,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2091,7 +2097,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2115,7 +2121,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2139,7 +2145,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2163,7 +2169,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2187,7 +2193,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2211,7 +2217,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2235,7 +2241,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2259,7 +2265,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2283,7 +2289,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2307,7 +2313,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -2331,7 +2337,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -2355,7 +2361,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -2379,7 +2385,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2403,7 +2409,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2427,7 +2433,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2451,7 +2457,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -2459,18 +2465,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="17">
+      <c r="E35" s="19">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -2479,7 +2485,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="17">
+      <c r="F36" s="19">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -2487,7 +2493,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -2496,11 +2502,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="17">
+      <c r="F38" s="19">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -2664,7 +2670,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -2688,7 +2694,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2712,7 +2718,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -2736,7 +2742,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -2760,7 +2766,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -2784,7 +2790,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -2808,7 +2814,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -2832,7 +2838,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2856,7 +2862,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -2880,7 +2886,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -2904,7 +2910,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -2928,7 +2934,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -2952,7 +2958,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -2976,7 +2982,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -3000,7 +3006,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -3024,7 +3030,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -3048,7 +3054,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -3072,7 +3078,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3096,7 +3102,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -3120,7 +3126,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -3128,18 +3134,18 @@
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="17">
+      <c r="E35" s="19">
         <f>SUM(E16:E34)</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="19">
         <f>SUM(F16:F34)</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -3148,7 +3154,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="17">
+      <c r="F36" s="19">
         <f>F35/E35*100</f>
         <v/>
       </c>
@@ -3156,7 +3162,7 @@
     </row>
     <row r="37" ht="9.75" customHeight="1"/>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -3165,11 +3171,11 @@
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="17">
+      <c r="F38" s="19">
         <f>F36*30/100</f>
         <v/>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3196,7 +3202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -3255,10 +3261,6 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3268,13 +3270,9 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Embedded/electronics lab (approx. for 25 trainees) with benches, storage and stationery</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="12" t="n"/>
+          <t>Computer Lab (400 sft) and Electronics Workshop/Laboratory (700–800 sft) for 25 trainees</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3333,12 +3331,12 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="20" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Computer/Laptop (1 unit) — trainer station</t>
+          <t>Computer/Laptop (Trainer)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
@@ -3357,12 +3355,12 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="20" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Multimedia projector &amp; screen (1 unit)</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="C17" s="9" t="n">
@@ -3372,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -3381,12 +3379,12 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="20" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Printer (1 unit)</t>
+          <t>Multimedia Projector</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
@@ -3396,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -3405,12 +3403,12 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="20" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Desktop/Laptop workstations (25 units) with internet access</t>
+          <t>High-performance Desktop/Laptop</t>
         </is>
       </c>
       <c r="C19" s="9" t="n">
@@ -3429,22 +3427,22 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="20" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Embedded / electronics laboratory (for 25 trainees)</t>
+          <t>Embedded IDE and Toolchain Software (Arduino IDE / STM32CubeIDE / PlatformIO or equivalent)</t>
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -3453,22 +3451,22 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="20" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Embedded development boards — Arduino, ESP32, STM32, Raspberry Pi Pico or equivalent (per trainee)</t>
+          <t>EDA/PCB Design Software (Schematic Capture and PCB Layout)</t>
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -3477,12 +3475,12 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="20" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Embedded IDEs / toolchains — Arduino IDE, PlatformIO, STM32CubeIDE, Wokwi or vendor SDK (25)</t>
+          <t>MCU Development Boards (STM32 / ESP32 / Arduino / RP2040 or equivalent)</t>
         </is>
       </c>
       <c r="C22" s="9" t="n">
@@ -3501,16 +3499,16 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="20" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Sensor modules — temperature, humidity, motion/IMU, current, light/optical, environmental</t>
+          <t>Sensor and Interface Module Kits (Temperature, Humidity, Pressure, IMU, Light, Gas, Display, Relay, etc.)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>0</v>
@@ -3525,22 +3523,22 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="20" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Communication/interface modules and displays (OLED/LCD; UART/I2C/SPI/RS232/RS485)</t>
+          <t>Breadboard and Electronic Component Kits</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -3549,12 +3547,12 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="20" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>PCB design tools — KiCad, EasyEDA, Altium or equivalent EDA tools (25)</t>
+          <t>JTAG/SWD Debugger/Programmer</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
@@ -3573,22 +3571,22 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="16" t="n">
+      <c r="A26" s="20" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Digital oscilloscope (per bench)</t>
+          <t>Digital Multimeter</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -3597,22 +3595,22 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="16" t="n">
+      <c r="A27" s="20" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Logic analyzer with protocol decoding (per bench)</t>
+          <t>ESD-safe Workbench with ESD Mat and Wrist Strap</t>
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -3621,16 +3619,16 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="16" t="n">
+      <c r="A28" s="20" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>JTAG/SWD debugger (per bench)</t>
+          <t>Digital Storage Oscilloscope</t>
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D28" s="9" t="n">
         <v>0</v>
@@ -3645,22 +3643,22 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="20" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Digital multimeters and adjustable power supplies (per bench)</t>
+          <t>Logic Analyzer</t>
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" s="9">
         <f>IFERROR(MIN(C29,D29)*E29/C29,0)</f>
@@ -3669,22 +3667,22 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="16" t="n">
+      <c r="A30" s="20" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Semiconductor devices — MCUs, sensor ICs, LDO/switching regulators, MOSFETs, level shifters, ESD protection</t>
+          <t>DC Regulated Power Supply</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -3693,22 +3691,22 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="20" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Breadboards, prototyping boards, basic components and hand tools</t>
+          <t>Soldering Station with Fume Extractor</t>
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" s="9">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
@@ -3717,22 +3715,22 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="20" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Soldering and assembly stations with ESD protection (per bench)</t>
+          <t>Function Generator</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -3741,16 +3739,16 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="20" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>PPE, ESD mat and wrist strap; first-aid and fire-safety equipment</t>
+          <t>Current Probe/Power Profiling Tool</t>
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>0</v>
@@ -3765,12 +3763,12 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="16" t="n">
+      <c r="A34" s="20" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Serial terminals, USB-serial adapters and cabling</t>
+          <t>PCB Prototype Fabrication and Assembly Support (In-house or Outsourced)</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
@@ -3780,65 +3778,145 @@
         <v>0</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(MIN(C34,D34)*E34/C34,0)</f>
         <v/>
       </c>
-      <c r="G34" s="9" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>01 set</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="14.15" customHeight="1">
+      <c r="A35" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Internet Connectivity with Network Switch and Router</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="9">
+        <f>IFERROR(MIN(C35,D35)*E35/C35,0)</f>
+        <v/>
+      </c>
+      <c r="G35" s="9" t="n"/>
+    </row>
+    <row r="36" ht="14.15" customHeight="1">
+      <c r="A36" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Central File/Storage Server</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" s="9">
+        <f>IFERROR(MIN(C36,D36)*E36/C36,0)</f>
+        <v/>
+      </c>
+      <c r="G36" s="9" t="n"/>
+    </row>
+    <row r="37" ht="14.15" customHeight="1">
+      <c r="A37" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>First Aid and Fire Safety Equipment</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="9">
+        <f>IFERROR(MIN(C37,D37)*E37/C37,0)</f>
+        <v/>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>01 set</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>Sum</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="17">
-        <f>SUM(E16:E34)</f>
-        <v/>
-      </c>
-      <c r="F35" s="17">
-        <f>SUM(F16:F34)</f>
-        <v/>
-      </c>
-      <c r="G35" s="13" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>Score out of 100</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="17">
-        <f>F35/E35*100</f>
-        <v/>
-      </c>
-      <c r="G36" s="13" t="n"/>
-    </row>
-    <row r="37" ht="9.75" customHeight="1"/>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
       </c>
       <c r="B38" s="11" t="n"/>
       <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="17">
-        <f>F36*30/100</f>
-        <v/>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="21">
+        <f>SUM(E16:E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="21">
+        <f>SUM(F16:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>Score out of 100</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="21">
+        <f>F38/E38*100</f>
+        <v/>
+      </c>
+      <c r="G39" s="13" t="n"/>
+    </row>
+    <row r="40" ht="9.75" customHeight="1"/>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total achieved points out of 30  </t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="21">
+        <f>F39*30/100</f>
+        <v/>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -3847,13 +3925,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3924,6 +4002,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3936,6 +4018,10 @@
           <t>Computer Lab (400 sft) and Test &amp; Measurement Laboratory (700–800 sft) for 25 trainees</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
